--- a/tests/test_results.xlsx
+++ b/tests/test_results.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055" activeTab="3"/>
+    <workbookView windowWidth="19200" windowHeight="8055"/>
   </bookViews>
   <sheets>
     <sheet name="预期" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
     <t>预期原因</t>
   </si>
   <si>
-    <t>错误发票_税额错误</t>
+    <t>error_tax_amount</t>
   </si>
   <si>
     <t>110102345678</t>
@@ -97,7 +97,7 @@
     <t>税额不符</t>
   </si>
   <si>
-    <t>错误发票_号码重复</t>
+    <t>error_duplicate</t>
   </si>
   <si>
     <t>1100143160</t>
@@ -115,7 +115,7 @@
     <t>号码重复</t>
   </si>
   <si>
-    <t>错误发票_价税合计</t>
+    <t>error_total</t>
   </si>
   <si>
     <t>2024060201</t>
@@ -130,7 +130,7 @@
     <t>价税合计不符</t>
   </si>
   <si>
-    <t>错误发票_税率错误</t>
+    <t>error_tax_rate</t>
   </si>
   <si>
     <t>2024060202</t>
@@ -145,7 +145,7 @@
     <t>税率非法</t>
   </si>
   <si>
-    <t>正常发票_旋转阴影</t>
+    <t>normal_rotated</t>
   </si>
   <si>
     <t>01234576</t>
@@ -160,7 +160,7 @@
     <t>通过</t>
   </si>
   <si>
-    <t>正常发票1</t>
+    <t>normal_1</t>
   </si>
   <si>
     <t>上海远景办公设备有限公司</t>
@@ -169,7 +169,7 @@
     <t>91310115MA1F2G3H4J</t>
   </si>
   <si>
-    <t>正常发票2</t>
+    <t>normal_2</t>
   </si>
   <si>
     <t>1100143168</t>
@@ -184,7 +184,7 @@
     <t>91110108MA0B7C8D9E</t>
   </si>
   <si>
-    <t>正常发票3</t>
+    <t>normal_3</t>
   </si>
   <si>
     <t>1100143161</t>
@@ -199,7 +199,7 @@
     <t>91320594MA3Q7B2L8K</t>
   </si>
   <si>
-    <t>正常发票4</t>
+    <t>normal_4</t>
   </si>
   <si>
     <t>1100143162</t>
@@ -208,7 +208,7 @@
     <t>01234569</t>
   </si>
   <si>
-    <t>正常发票5</t>
+    <t>normal_5</t>
   </si>
   <si>
     <t>1100143163</t>
@@ -223,7 +223,7 @@
     <t>91440101MA5CL8D27H</t>
   </si>
   <si>
-    <t>正常发票6</t>
+    <t>normal_6</t>
   </si>
   <si>
     <t>1100143164</t>
@@ -238,7 +238,7 @@
     <t>91440300MA5K1L2M3N</t>
   </si>
   <si>
-    <t>正常发票7</t>
+    <t>normal_7</t>
   </si>
   <si>
     <t>1100143165</t>
@@ -253,7 +253,7 @@
     <t>91120116MA06P3K9H2</t>
   </si>
   <si>
-    <t>正常发票8</t>
+    <t>normal_8</t>
   </si>
   <si>
     <t>1100143166</t>
@@ -268,7 +268,7 @@
     <t>91330109MA2B1C3D4E</t>
   </si>
   <si>
-    <t>正常发票9</t>
+    <t>normal_9</t>
   </si>
   <si>
     <t>1100143167</t>
@@ -283,7 +283,7 @@
     <t>91330212MA2J5K6L7M</t>
   </si>
   <si>
-    <t>正常发票10</t>
+    <t>normal_10</t>
   </si>
   <si>
     <t>北京华创办公设备有限公司</t>
@@ -2021,7 +2021,7 @@
     <row r="2" spans="1:13">
       <c r="A2" t="str">
         <f>预期!A2</f>
-        <v>错误发票_税额错误</v>
+        <v>error_tax_amount</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>14</v>
@@ -2063,7 +2063,7 @@
     <row r="3" spans="1:13">
       <c r="A3" t="str">
         <f>预期!A3</f>
-        <v>错误发票_号码重复</v>
+        <v>error_duplicate</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>21</v>
@@ -2105,7 +2105,7 @@
     <row r="4" spans="1:13">
       <c r="A4" t="str">
         <f>预期!A4</f>
-        <v>错误发票_价税合计</v>
+        <v>error_total</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2147,7 +2147,7 @@
     <row r="5" spans="1:13">
       <c r="A5" t="str">
         <f>预期!A5</f>
-        <v>错误发票_税率错误</v>
+        <v>error_tax_rate</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>32</v>
@@ -2189,7 +2189,7 @@
     <row r="6" spans="1:13">
       <c r="A6" t="str">
         <f>预期!A6</f>
-        <v>正常发票_旋转阴影</v>
+        <v>normal_rotated</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>21</v>
@@ -2228,7 +2228,7 @@
     <row r="7" spans="1:13">
       <c r="A7" t="str">
         <f>预期!A7</f>
-        <v>正常发票1</v>
+        <v>normal_1</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>21</v>
@@ -2267,7 +2267,7 @@
     <row r="8" spans="1:13">
       <c r="A8" t="str">
         <f>预期!A8</f>
-        <v>正常发票2</v>
+        <v>normal_2</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>45</v>
@@ -2306,7 +2306,7 @@
     <row r="9" spans="1:13">
       <c r="A9" t="str">
         <f>预期!A9</f>
-        <v>正常发票3</v>
+        <v>normal_3</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>50</v>
@@ -2345,7 +2345,7 @@
     <row r="10" spans="1:13">
       <c r="A10" t="str">
         <f>预期!A10</f>
-        <v>正常发票4</v>
+        <v>normal_4</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>55</v>
@@ -2384,7 +2384,7 @@
     <row r="11" spans="1:13">
       <c r="A11" t="str">
         <f>预期!A11</f>
-        <v>正常发票5</v>
+        <v>normal_5</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>58</v>
@@ -2423,7 +2423,7 @@
     <row r="12" spans="1:13">
       <c r="A12" t="str">
         <f>预期!A12</f>
-        <v>正常发票6</v>
+        <v>normal_6</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>63</v>
@@ -2462,7 +2462,7 @@
     <row r="13" spans="1:13">
       <c r="A13" t="str">
         <f>预期!A13</f>
-        <v>正常发票7</v>
+        <v>normal_7</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>68</v>
@@ -2501,7 +2501,7 @@
     <row r="14" spans="1:13">
       <c r="A14" t="str">
         <f>预期!A14</f>
-        <v>正常发票8</v>
+        <v>normal_8</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>73</v>
@@ -2540,7 +2540,7 @@
     <row r="15" spans="1:13">
       <c r="A15" t="str">
         <f>预期!A15</f>
-        <v>正常发票9</v>
+        <v>normal_9</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>78</v>
@@ -2579,7 +2579,7 @@
     <row r="16" spans="1:13">
       <c r="A16" t="str">
         <f>预期!A16</f>
-        <v>正常发票10</v>
+        <v>normal_10</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>21</v>
@@ -2685,7 +2685,7 @@
     <row r="5" spans="1:12">
       <c r="A5" t="str">
         <f>实际!A2</f>
-        <v>错误发票_税额错误</v>
+        <v>error_tax_amount</v>
       </c>
       <c r="B5">
         <f>IF(预期!B2=实际!B2,1,0)</f>
@@ -2735,7 +2735,7 @@
     <row r="6" spans="1:12">
       <c r="A6" t="str">
         <f>实际!A3</f>
-        <v>错误发票_号码重复</v>
+        <v>error_duplicate</v>
       </c>
       <c r="B6">
         <f>IF(预期!B3=实际!B3,1,0)</f>
@@ -2785,7 +2785,7 @@
     <row r="7" spans="1:12">
       <c r="A7" t="str">
         <f>实际!A4</f>
-        <v>错误发票_价税合计</v>
+        <v>error_total</v>
       </c>
       <c r="B7">
         <f>IF(预期!B4=实际!B4,1,0)</f>
@@ -2835,7 +2835,7 @@
     <row r="8" spans="1:12">
       <c r="A8" t="str">
         <f>实际!A5</f>
-        <v>错误发票_税率错误</v>
+        <v>error_tax_rate</v>
       </c>
       <c r="B8">
         <f>IF(预期!B5=实际!B5,1,0)</f>
@@ -2885,7 +2885,7 @@
     <row r="9" spans="1:12">
       <c r="A9" t="str">
         <f>实际!A6</f>
-        <v>正常发票_旋转阴影</v>
+        <v>normal_rotated</v>
       </c>
       <c r="B9">
         <f>IF(预期!B6=实际!B6,1,0)</f>
@@ -2935,7 +2935,7 @@
     <row r="10" spans="1:12">
       <c r="A10" t="str">
         <f>实际!A7</f>
-        <v>正常发票1</v>
+        <v>normal_1</v>
       </c>
       <c r="B10">
         <f>IF(预期!B7=实际!B7,1,0)</f>
@@ -2985,7 +2985,7 @@
     <row r="11" spans="1:12">
       <c r="A11" t="str">
         <f>实际!A8</f>
-        <v>正常发票2</v>
+        <v>normal_2</v>
       </c>
       <c r="B11">
         <f>IF(预期!B8=实际!B8,1,0)</f>
@@ -3035,7 +3035,7 @@
     <row r="12" spans="1:12">
       <c r="A12" t="str">
         <f>实际!A9</f>
-        <v>正常发票3</v>
+        <v>normal_3</v>
       </c>
       <c r="B12">
         <f>IF(预期!B9=实际!B9,1,0)</f>
@@ -3085,7 +3085,7 @@
     <row r="13" spans="1:12">
       <c r="A13" t="str">
         <f>实际!A10</f>
-        <v>正常发票4</v>
+        <v>normal_4</v>
       </c>
       <c r="B13">
         <f>IF(预期!B10=实际!B10,1,0)</f>
@@ -3135,7 +3135,7 @@
     <row r="14" spans="1:12">
       <c r="A14" t="str">
         <f>实际!A11</f>
-        <v>正常发票5</v>
+        <v>normal_5</v>
       </c>
       <c r="B14">
         <f>IF(预期!B11=实际!B11,1,0)</f>
@@ -3185,7 +3185,7 @@
     <row r="15" spans="1:12">
       <c r="A15" t="str">
         <f>实际!A12</f>
-        <v>正常发票6</v>
+        <v>normal_6</v>
       </c>
       <c r="B15">
         <f>IF(预期!B12=实际!B12,1,0)</f>
@@ -3235,7 +3235,7 @@
     <row r="16" spans="1:12">
       <c r="A16" t="str">
         <f>实际!A13</f>
-        <v>正常发票7</v>
+        <v>normal_7</v>
       </c>
       <c r="B16">
         <f>IF(预期!B13=实际!B13,1,0)</f>
@@ -3285,7 +3285,7 @@
     <row r="17" spans="1:12">
       <c r="A17" t="str">
         <f>实际!A14</f>
-        <v>正常发票8</v>
+        <v>normal_8</v>
       </c>
       <c r="B17">
         <f>IF(预期!B14=实际!B14,1,0)</f>
@@ -3335,7 +3335,7 @@
     <row r="18" spans="1:12">
       <c r="A18" t="str">
         <f>实际!A15</f>
-        <v>正常发票9</v>
+        <v>normal_9</v>
       </c>
       <c r="B18">
         <f>IF(预期!B15=实际!B15,1,0)</f>
@@ -3385,7 +3385,7 @@
     <row r="19" spans="1:12">
       <c r="A19" t="str">
         <f>实际!A16</f>
-        <v>正常发票10</v>
+        <v>normal_10</v>
       </c>
       <c r="B19">
         <f>IF(预期!B16=实际!B16,1,0)</f>
